--- a/data/Data PDRB.xlsx
+++ b/data/Data PDRB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats_flutter\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats-data-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCCE398-D8B2-4881-9BE4-2920979CC305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1C7E99-9A11-4388-935A-F0E9D42AB657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DDEFA1D-E8F3-42A2-94D5-6A9B3C26F462}"/>
   </bookViews>
@@ -48,12 +48,6 @@
     <t>PDRB</t>
   </si>
   <si>
-    <t>2023 Angka Sementara</t>
-  </si>
-  <si>
-    <t>2024 Angka Sangat Sementara</t>
-  </si>
-  <si>
     <t>LPE</t>
   </si>
   <si>
@@ -718,6 +712,12 @@
   </si>
   <si>
     <t>3.39</t>
+  </si>
+  <si>
+    <t>2024 Angka Sementara</t>
+  </si>
+  <si>
+    <t>2025 Angka Sangat Sementara</t>
   </si>
 </sst>
 </file>
@@ -827,7 +827,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -891,12 +891,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1436,7 +1430,7 @@
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>3</v>
@@ -1455,13 +1449,12 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
-      <c r="Q6" s="11" t="s">
-        <v>4</v>
-      </c>
       <c r="R6" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="S6" s="11"/>
+        <v>226</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>227</v>
+      </c>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1474,56 +1467,56 @@
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="E7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="F7" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="H7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="I7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="J7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="K7" s="14" t="s">
         <v>13</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>15</v>
       </c>
       <c r="L7" s="15">
         <v>45936</v>
       </c>
-      <c r="M7" s="28"/>
+      <c r="M7" s="14"/>
       <c r="N7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="14" t="s">
+      <c r="R7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="R7" s="18" t="s">
-        <v>19</v>
-      </c>
       <c r="S7" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="T7" s="19"/>
       <c r="U7" s="19"/>
@@ -1537,7 +1530,7 @@
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="12"/>
@@ -1568,58 +1561,58 @@
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="G9" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="18" t="s">
+      <c r="H9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="I9" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="L9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="M9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="N9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="O9" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="L9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" s="18" t="s">
-        <v>28</v>
-      </c>
       <c r="R9" s="18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="S9" s="18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T9" s="19"/>
       <c r="U9" s="19"/>
@@ -1633,55 +1626,55 @@
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S10" s="18"/>
       <c r="T10" s="19"/>
@@ -1696,58 +1689,58 @@
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="F11" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="G11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="H11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="I11" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="J11" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="K11" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="L11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="M11" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="N11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="O11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="P11" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="O11" s="18" t="s">
+      <c r="Q11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="P11" s="18" t="s">
+      <c r="R11" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="Q11" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="R11" s="18" t="s">
-        <v>45</v>
-      </c>
       <c r="S11" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="T11" s="19"/>
       <c r="U11" s="19"/>
@@ -1761,58 +1754,58 @@
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="F12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="G12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="H12" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="I12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="J12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="K12" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="M12" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K12" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="L12" s="18" t="s">
+      <c r="N12" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="M12" s="18" t="s">
+      <c r="O12" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="18" t="s">
+      <c r="P12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="O12" s="18" t="s">
+      <c r="Q12" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="P12" s="18" t="s">
+      <c r="R12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="Q12" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="R12" s="18" t="s">
-        <v>60</v>
-      </c>
       <c r="S12" s="18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="T12" s="19"/>
       <c r="U12" s="19"/>
@@ -1826,58 +1819,58 @@
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21"/>
       <c r="B13" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>63</v>
-      </c>
       <c r="K13" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R13" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S13" s="18" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T13" s="21"/>
       <c r="U13" s="21"/>
@@ -1891,58 +1884,58 @@
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="F14" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="G14" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="H14" s="18" t="s">
         <v>67</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>69</v>
       </c>
       <c r="I14" s="17">
         <v>45789</v>
       </c>
       <c r="J14" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="M14" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="N14" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="18" t="s">
+      <c r="O14" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="N14" s="18" t="s">
+      <c r="P14" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="O14" s="18" t="s">
+      <c r="Q14" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="P14" s="18" t="s">
+      <c r="R14" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q14" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="R14" s="18" t="s">
-        <v>78</v>
-      </c>
       <c r="S14" s="18" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -1956,58 +1949,58 @@
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>81</v>
       </c>
       <c r="F15" s="17">
         <v>45732</v>
       </c>
       <c r="G15" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="J15" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="K15" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="L15" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="M15" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="L15" s="18" t="s">
+      <c r="N15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="18" t="s">
+      <c r="O15" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="P15" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="N15" s="18" t="s">
+      <c r="Q15" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="O15" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="P15" s="18" t="s">
+      <c r="R15" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="Q15" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="R15" s="18" t="s">
-        <v>92</v>
-      </c>
       <c r="S15" s="18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -2021,58 +2014,58 @@
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="F16" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="G16" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="H16" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="I16" s="18" t="s">
         <v>97</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>99</v>
       </c>
       <c r="J16" s="17">
         <v>45663</v>
       </c>
       <c r="K16" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="M16" s="18" t="s">
-        <v>102</v>
       </c>
       <c r="N16" s="17">
         <v>45905</v>
       </c>
       <c r="O16" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="P16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q16" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="R16" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="P16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q16" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="R16" s="18" t="s">
-        <v>105</v>
-      </c>
       <c r="S16" s="18" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -2086,58 +2079,58 @@
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="F17" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="G17" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="H17" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="I17" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="K17" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="18" t="s">
+      <c r="L17" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="M17" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="N17" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="O17" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="M17" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="N17" s="18" t="s">
+      <c r="P17" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="O17" s="18" t="s">
+      <c r="Q17" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="P17" s="18" t="s">
+      <c r="R17" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="Q17" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="R17" s="18" t="s">
-        <v>119</v>
-      </c>
       <c r="S17" s="18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -2151,58 +2144,58 @@
     <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="F18" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="G18" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="H18" s="18" t="s">
         <v>123</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>125</v>
       </c>
       <c r="I18" s="22">
         <v>45934</v>
       </c>
       <c r="J18" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="M18" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="N18" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="K18" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="L18" s="18" t="s">
+      <c r="O18" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="M18" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="N18" s="18" t="s">
+      <c r="P18" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="O18" s="18" t="s">
+      <c r="Q18" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="P18" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q18" s="18" t="s">
-        <v>131</v>
-      </c>
       <c r="R18" s="18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S18" s="18" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
@@ -2216,58 +2209,58 @@
     <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="12" t="s">
+      <c r="F19" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="G19" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="H19" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="I19" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="18" t="s">
+      <c r="J19" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="K19" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="L19" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="N19" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="J19" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="K19" s="18" t="s">
+      <c r="O19" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="L19" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="M19" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="N19" s="18" t="s">
+      <c r="P19" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="O19" s="18" t="s">
+      <c r="Q19" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="P19" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q19" s="18" t="s">
-        <v>143</v>
-      </c>
       <c r="R19" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="S19" s="18" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
@@ -2281,22 +2274,22 @@
     <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="12" t="s">
+      <c r="F20" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="G20" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>148</v>
       </c>
       <c r="H20" s="22">
         <v>45966</v>
@@ -2305,34 +2298,34 @@
         <v>45782</v>
       </c>
       <c r="J20" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="L20" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="M20" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="L20" s="18" t="s">
+      <c r="N20" s="18" t="s">
         <v>151</v>
-      </c>
-      <c r="M20" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="N20" s="18" t="s">
-        <v>153</v>
       </c>
       <c r="O20" s="22">
         <v>45935</v>
       </c>
       <c r="P20" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Q20" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="R20" s="18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S20" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
@@ -2346,58 +2339,58 @@
     <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="12" t="s">
+      <c r="G21" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="18" t="s">
+      <c r="H21" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="G21" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>159</v>
-      </c>
       <c r="J21" s="18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K21" s="22">
         <v>45935</v>
       </c>
       <c r="L21" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="N21" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="M21" s="18" t="s">
+      <c r="O21" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="N21" s="18" t="s">
+      <c r="P21" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q21" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="O21" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="P21" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q21" s="18" t="s">
-        <v>164</v>
-      </c>
       <c r="R21" s="18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="S21" s="18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
@@ -2411,34 +2404,34 @@
     <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="12" t="s">
+      <c r="F22" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="I22" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F22" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="H22" s="18" t="s">
+      <c r="J22" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="K22" s="18" t="s">
         <v>169</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>171</v>
       </c>
       <c r="L22" s="17">
         <v>45692</v>
@@ -2450,19 +2443,19 @@
         <v>45904</v>
       </c>
       <c r="O22" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q22" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="P22" s="18" t="s">
+      <c r="R22" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="Q22" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="R22" s="18" t="s">
-        <v>175</v>
-      </c>
       <c r="S22" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
@@ -2476,58 +2469,58 @@
     <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="F23" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="G23" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="I23" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="G23" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H23" s="18" t="s">
+      <c r="J23" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="K23" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="J23" s="18" t="s">
+      <c r="L23" s="18" t="s">
         <v>182</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>184</v>
       </c>
       <c r="M23" s="17">
         <v>45664</v>
       </c>
       <c r="N23" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="O23" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="P23" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="O23" s="18" t="s">
+      <c r="Q23" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="P23" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q23" s="18" t="s">
-        <v>188</v>
-      </c>
       <c r="R23" s="18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S23" s="18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -2541,58 +2534,58 @@
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="I24" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F24" s="18" t="s">
+      <c r="J24" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="G24" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="I24" s="18" t="s">
+      <c r="K24" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="M24" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="J24" s="18" t="s">
+      <c r="N24" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="K24" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="M24" s="18" t="s">
+      <c r="O24" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="N24" s="18" t="s">
+      <c r="P24" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="Q24" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="P24" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q24" s="18" t="s">
-        <v>197</v>
-      </c>
       <c r="R24" s="18" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="S24" s="18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -2606,37 +2599,37 @@
     <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="12" t="s">
+      <c r="F25" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="G25" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="H25" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="I25" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="J25" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="K25" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="J25" s="18" t="s">
+      <c r="L25" s="18" t="s">
         <v>205</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>207</v>
       </c>
       <c r="M25" s="17">
         <v>45691</v>
@@ -2645,19 +2638,19 @@
         <v>45811</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P25" s="17">
         <v>45841</v>
       </c>
       <c r="Q25" s="18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="R25" s="18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S25" s="18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -2674,55 +2667,55 @@
         <v>3</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="S26" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>

--- a/data/Data PDRB.xlsx
+++ b/data/Data PDRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats-data-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1C7E99-9A11-4388-935A-F0E9D42AB657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8C9B18-B3A3-494E-8F0D-7F95557CEB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DDEFA1D-E8F3-42A2-94D5-6A9B3C26F462}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="27">
   <si>
     <t>DATA STRATEGIS KOTA JAKARTA TIMUR 2010 - 2025</t>
   </si>
@@ -57,64 +57,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>6.28</t>
-  </si>
-  <si>
-    <t>6.13</t>
-  </si>
-  <si>
-    <t>5.89</t>
-  </si>
-  <si>
-    <t>6.14</t>
-  </si>
-  <si>
-    <t>5.50</t>
-  </si>
-  <si>
-    <t>6.15</t>
-  </si>
-  <si>
-    <t>6.25</t>
-  </si>
-  <si>
-    <t>(4.47)</t>
-  </si>
-  <si>
-    <t>4.77</t>
-  </si>
-  <si>
-    <t>5.15</t>
-  </si>
-  <si>
-    <t>4.49</t>
-  </si>
-  <si>
     <t>Kontribusi Lapangan usaha dalam struktur ekonomi Jakarta Timur</t>
   </si>
   <si>
     <t>A. Pertanian, Kehutanan, dan Perikanan</t>
-  </si>
-  <si>
-    <t>0.13</t>
-  </si>
-  <si>
-    <t>0.12</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>0.07</t>
   </si>
   <si>
     <t>B. Pertambangan dan Penggalian</t>
@@ -123,595 +69,46 @@
     <t>C. Industri Pengolahan</t>
   </si>
   <si>
-    <t>32.00</t>
-  </si>
-  <si>
-    <t>31.36</t>
-  </si>
-  <si>
-    <t>31.17</t>
-  </si>
-  <si>
-    <t>30.77</t>
-  </si>
-  <si>
-    <t>30.24</t>
-  </si>
-  <si>
-    <t>30.28</t>
-  </si>
-  <si>
-    <t>29.68</t>
-  </si>
-  <si>
-    <t>29.62</t>
-  </si>
-  <si>
-    <t>28.86</t>
-  </si>
-  <si>
-    <t>27.54</t>
-  </si>
-  <si>
-    <t>26.61</t>
-  </si>
-  <si>
-    <t>28.24</t>
-  </si>
-  <si>
-    <t>28.38</t>
-  </si>
-  <si>
-    <t>27.25</t>
-  </si>
-  <si>
-    <t>26.73</t>
-  </si>
-  <si>
     <t>D. Pengadaan Listrik dan Gas</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>0.24</t>
   </si>
   <si>
     <t>E. Pengadaan Air, Pengelolaan Sampah, Limbah dan Daur Ulang</t>
   </si>
   <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
     <t>F. Konstruksi</t>
-  </si>
-  <si>
-    <t>12.77</t>
-  </si>
-  <si>
-    <t>12.74</t>
-  </si>
-  <si>
-    <t>12.86</t>
-  </si>
-  <si>
-    <t>12.80</t>
-  </si>
-  <si>
-    <t>12.29</t>
-  </si>
-  <si>
-    <t>11.40</t>
-  </si>
-  <si>
-    <t>11.25</t>
-  </si>
-  <si>
-    <t>11.15</t>
-  </si>
-  <si>
-    <t>10.92</t>
-  </si>
-  <si>
-    <t>10.81</t>
-  </si>
-  <si>
-    <t>10.61</t>
-  </si>
-  <si>
-    <t>10.48</t>
-  </si>
-  <si>
-    <t>10.24</t>
-  </si>
-  <si>
-    <t>10.34</t>
   </si>
   <si>
     <t>G. Perdagangan Besar dan Eceran; Reparasi Mobil dan Sepeda Motor</t>
   </si>
   <si>
-    <t>16.22</t>
-  </si>
-  <si>
-    <t>16.35</t>
-  </si>
-  <si>
-    <t>16.39</t>
-  </si>
-  <si>
-    <t>16.62</t>
-  </si>
-  <si>
-    <t>15.90</t>
-  </si>
-  <si>
-    <t>15.83</t>
-  </si>
-  <si>
-    <t>15.94</t>
-  </si>
-  <si>
-    <t>16.32</t>
-  </si>
-  <si>
-    <t>16.86</t>
-  </si>
-  <si>
-    <t>16.90</t>
-  </si>
-  <si>
-    <t>17.56</t>
-  </si>
-  <si>
-    <t>17.77</t>
-  </si>
-  <si>
-    <t>18.21</t>
-  </si>
-  <si>
     <t>H. Transportasi dan Pergudangan</t>
-  </si>
-  <si>
-    <t>3.00</t>
-  </si>
-  <si>
-    <t>2.98</t>
-  </si>
-  <si>
-    <t>2.96</t>
-  </si>
-  <si>
-    <t>3.19</t>
-  </si>
-  <si>
-    <t>4.31</t>
-  </si>
-  <si>
-    <t>4.97</t>
-  </si>
-  <si>
-    <t>6.30</t>
-  </si>
-  <si>
-    <t>6.38</t>
-  </si>
-  <si>
-    <t>6.44</t>
-  </si>
-  <si>
-    <t>5.20</t>
-  </si>
-  <si>
-    <t>6.70</t>
-  </si>
-  <si>
-    <t>6.82</t>
   </si>
   <si>
     <t>I. Penyediaan Akomodasi dan Makan Minum</t>
   </si>
   <si>
-    <t>4.62</t>
-  </si>
-  <si>
-    <t>4.69</t>
-  </si>
-  <si>
-    <t>4.78</t>
-  </si>
-  <si>
-    <t>4.82</t>
-  </si>
-  <si>
-    <t>4.84</t>
-  </si>
-  <si>
-    <t>4.67</t>
-  </si>
-  <si>
-    <t>4.57</t>
-  </si>
-  <si>
-    <t>4.46</t>
-  </si>
-  <si>
-    <t>4.21</t>
-  </si>
-  <si>
-    <t>4.38</t>
-  </si>
-  <si>
-    <t>4.52</t>
-  </si>
-  <si>
-    <t>4.70</t>
-  </si>
-  <si>
-    <t>4.89</t>
-  </si>
-  <si>
     <t>J. Informasi dan Komunikasi</t>
-  </si>
-  <si>
-    <t>4.39</t>
-  </si>
-  <si>
-    <t>4.32</t>
-  </si>
-  <si>
-    <t>4.42</t>
-  </si>
-  <si>
-    <t>4.41</t>
-  </si>
-  <si>
-    <t>4.22</t>
-  </si>
-  <si>
-    <t>4.14</t>
-  </si>
-  <si>
-    <t>4.53</t>
-  </si>
-  <si>
-    <t>5.61</t>
-  </si>
-  <si>
-    <t>5.57</t>
-  </si>
-  <si>
-    <t>5.53</t>
-  </si>
-  <si>
-    <t>5.56</t>
   </si>
   <si>
     <t>K.Jasa Keuangan dan Asuransi</t>
   </si>
   <si>
-    <t>1.59</t>
-  </si>
-  <si>
-    <t>1.53</t>
-  </si>
-  <si>
-    <t>1.62</t>
-  </si>
-  <si>
-    <t>1.64</t>
-  </si>
-  <si>
-    <t>1.55</t>
-  </si>
-  <si>
-    <t>1.57</t>
-  </si>
-  <si>
-    <t>1.61</t>
-  </si>
-  <si>
-    <t>1.78</t>
-  </si>
-  <si>
-    <t>1.73</t>
-  </si>
-  <si>
-    <t>1.71</t>
-  </si>
-  <si>
-    <t>1.70</t>
-  </si>
-  <si>
     <t>L. Real Estat</t>
-  </si>
-  <si>
-    <t>5.52</t>
-  </si>
-  <si>
-    <t>5.43</t>
-  </si>
-  <si>
-    <t>5.32</t>
-  </si>
-  <si>
-    <t>5.18</t>
-  </si>
-  <si>
-    <t>4.96</t>
-  </si>
-  <si>
-    <t>4.94</t>
-  </si>
-  <si>
-    <t>4.88</t>
-  </si>
-  <si>
-    <t>4.87</t>
-  </si>
-  <si>
-    <t>5.29</t>
-  </si>
-  <si>
-    <t>4.86</t>
   </si>
   <si>
     <t>M,N Jasa Perusahaan</t>
   </si>
   <si>
-    <t>4.40</t>
-  </si>
-  <si>
-    <t>4.43</t>
-  </si>
-  <si>
-    <t>4.51</t>
-  </si>
-  <si>
-    <t>4.64</t>
-  </si>
-  <si>
-    <t>5.28</t>
-  </si>
-  <si>
-    <t>5.70</t>
-  </si>
-  <si>
-    <t>5.99</t>
-  </si>
-  <si>
-    <t>5.69</t>
-  </si>
-  <si>
-    <t>5.85</t>
-  </si>
-  <si>
     <t>O. Administrasi Pemerintahan, Pertahanan dan Jaminan Sosial Wajib</t>
-  </si>
-  <si>
-    <t>4.00</t>
-  </si>
-  <si>
-    <t>4.60</t>
-  </si>
-  <si>
-    <t>4.29</t>
-  </si>
-  <si>
-    <t>4.25</t>
-  </si>
-  <si>
-    <t>4.19</t>
-  </si>
-  <si>
-    <t>3.79</t>
-  </si>
-  <si>
-    <t>3.72</t>
-  </si>
-  <si>
-    <t>3.50</t>
-  </si>
-  <si>
-    <t>3.29</t>
-  </si>
-  <si>
-    <t>3.26</t>
   </si>
   <si>
     <t>P. Jasa Pendidikan</t>
   </si>
   <si>
-    <t>6.88</t>
-  </si>
-  <si>
-    <t>6.77</t>
-  </si>
-  <si>
-    <t>6.84</t>
-  </si>
-  <si>
-    <t>7.00</t>
-  </si>
-  <si>
-    <t>7.38</t>
-  </si>
-  <si>
-    <t>7.68</t>
-  </si>
-  <si>
-    <t>7.25</t>
-  </si>
-  <si>
-    <t>7.13</t>
-  </si>
-  <si>
-    <t>7.55</t>
-  </si>
-  <si>
-    <t>7.17</t>
-  </si>
-  <si>
-    <t>6.68</t>
-  </si>
-  <si>
-    <t>6.20</t>
-  </si>
-  <si>
     <t>Q. Jasa Kesehatan dan Kegiatan Sosial</t>
   </si>
   <si>
-    <t>1.60</t>
-  </si>
-  <si>
-    <t>1.65</t>
-  </si>
-  <si>
-    <t>1.69</t>
-  </si>
-  <si>
-    <t>1.74</t>
-  </si>
-  <si>
-    <t>2.22</t>
-  </si>
-  <si>
-    <t>2.25</t>
-  </si>
-  <si>
-    <t>2.30</t>
-  </si>
-  <si>
-    <t>2.29</t>
-  </si>
-  <si>
     <t>R,S,TU Jasa lainnya</t>
-  </si>
-  <si>
-    <t>2.32</t>
-  </si>
-  <si>
-    <t>2.39</t>
-  </si>
-  <si>
-    <t>2.41</t>
-  </si>
-  <si>
-    <t>2.54</t>
-  </si>
-  <si>
-    <t>2.57</t>
-  </si>
-  <si>
-    <t>2.64</t>
-  </si>
-  <si>
-    <t>2.70</t>
-  </si>
-  <si>
-    <t>2.83</t>
-  </si>
-  <si>
-    <t>2.88</t>
-  </si>
-  <si>
-    <t>2.81</t>
-  </si>
-  <si>
-    <t>3.31</t>
-  </si>
-  <si>
-    <t>3.32</t>
-  </si>
-  <si>
-    <t>100.00</t>
-  </si>
-  <si>
-    <t>5.02</t>
-  </si>
-  <si>
-    <t>5.17</t>
-  </si>
-  <si>
-    <t>26.25</t>
-  </si>
-  <si>
-    <t>0.17</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>10.05</t>
-  </si>
-  <si>
-    <t>18.30</t>
-  </si>
-  <si>
-    <t>7.08</t>
-  </si>
-  <si>
-    <t>5.12</t>
-  </si>
-  <si>
-    <t>5.60</t>
-  </si>
-  <si>
-    <t>1.67</t>
-  </si>
-  <si>
-    <t>5.95</t>
-  </si>
-  <si>
-    <t>3.25</t>
-  </si>
-  <si>
-    <t>6.43</t>
-  </si>
-  <si>
-    <t>2.31</t>
-  </si>
-  <si>
-    <t>3.39</t>
   </si>
   <si>
     <t>2024 Angka Sementara</t>
@@ -724,10 +121,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="d\.m"/>
-    <numFmt numFmtId="165" formatCode="dd\.mm"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -769,7 +162,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -794,8 +187,14 @@
         <bgColor rgb="FFCCFF33"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFCCFF33"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -823,11 +222,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -861,15 +269,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -880,9 +279,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -891,6 +287,20 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1212,26 +622,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -1435,9 +845,9 @@
       <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -1445,15 +855,16 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
       <c r="R6" s="11" t="s">
-        <v>226</v>
+        <v>25</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>227</v>
+        <v>26</v>
       </c>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
@@ -1475,467 +886,467 @@
       <c r="D7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" s="15">
-        <v>45936</v>
+      <c r="E7" s="25">
+        <v>6.28</v>
+      </c>
+      <c r="F7" s="25">
+        <v>6.13</v>
+      </c>
+      <c r="G7" s="25">
+        <v>5.89</v>
+      </c>
+      <c r="H7" s="25">
+        <v>6.14</v>
+      </c>
+      <c r="I7" s="25">
+        <v>5.5</v>
+      </c>
+      <c r="J7" s="25">
+        <v>6.15</v>
+      </c>
+      <c r="K7" s="25">
+        <v>6.25</v>
+      </c>
+      <c r="L7" s="25">
+        <v>6.1</v>
       </c>
       <c r="M7" s="14"/>
-      <c r="N7" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="P7" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="R7" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
+      <c r="N7" s="26">
+        <v>-4.47</v>
+      </c>
+      <c r="O7" s="25">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="P7" s="27">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="Q7" s="25">
+        <v>5.15</v>
+      </c>
+      <c r="R7" s="27">
+        <v>4.49</v>
+      </c>
+      <c r="S7" s="25">
+        <v>5.17</v>
+      </c>
+      <c r="T7" s="16"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="16"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
-      <c r="B8" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="26"/>
+      <c r="B8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="22"/>
       <c r="D8" s="12"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="20"/>
+      <c r="Q8" s="17"/>
       <c r="R8" s="12"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="13" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="R9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
+      <c r="D9" s="28">
+        <v>0.13</v>
+      </c>
+      <c r="E9" s="27">
+        <v>0.13</v>
+      </c>
+      <c r="F9" s="27">
+        <v>0.12</v>
+      </c>
+      <c r="G9" s="27">
+        <v>0.11</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="J9" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="27">
+        <v>0.09</v>
+      </c>
+      <c r="L9" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="M9" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="N9" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="O9" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="P9" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="Q9" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R9" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S9" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="13" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="K10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="18" t="s">
+      <c r="N10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="O10" s="18" t="s">
+      <c r="O10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="18" t="s">
+      <c r="P10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="Q10" s="18" t="s">
+      <c r="Q10" s="15" t="s">
         <v>6</v>
       </c>
       <c r="R10" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="S10" s="18"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="13" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="18" t="s">
+      <c r="D11" s="28">
         <v>32</v>
       </c>
-      <c r="H11" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="N11" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="O11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="P11" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q11" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="R11" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
+      <c r="E11" s="27">
+        <v>31.36</v>
+      </c>
+      <c r="F11" s="27">
+        <v>31.17</v>
+      </c>
+      <c r="G11" s="27">
+        <v>30.77</v>
+      </c>
+      <c r="H11" s="27">
+        <v>30.24</v>
+      </c>
+      <c r="I11" s="27">
+        <v>30.28</v>
+      </c>
+      <c r="J11" s="27">
+        <v>29.68</v>
+      </c>
+      <c r="K11" s="27">
+        <v>29.62</v>
+      </c>
+      <c r="L11" s="27">
+        <v>28.86</v>
+      </c>
+      <c r="M11" s="27">
+        <v>27.54</v>
+      </c>
+      <c r="N11" s="27">
+        <v>26.61</v>
+      </c>
+      <c r="O11" s="27">
+        <v>28.24</v>
+      </c>
+      <c r="P11" s="27">
+        <v>28.38</v>
+      </c>
+      <c r="Q11" s="27">
+        <v>27.25</v>
+      </c>
+      <c r="R11" s="27">
+        <v>26.73</v>
+      </c>
+      <c r="S11" s="27">
+        <v>26.25</v>
+      </c>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="13" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="M12" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="N12" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="O12" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="P12" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q12" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="R12" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="S12" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
+      <c r="D12" s="28">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E12" s="27">
+        <v>0.69</v>
+      </c>
+      <c r="F12" s="27">
+        <v>0.74</v>
+      </c>
+      <c r="G12" s="27">
+        <v>0.65</v>
+      </c>
+      <c r="H12" s="27">
+        <v>0.62</v>
+      </c>
+      <c r="I12" s="27">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J12" s="27">
+        <v>0.54</v>
+      </c>
+      <c r="K12" s="27">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L12" s="27">
+        <v>0.67</v>
+      </c>
+      <c r="M12" s="27">
+        <v>0.72</v>
+      </c>
+      <c r="N12" s="27">
+        <v>0.66</v>
+      </c>
+      <c r="O12" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="P12" s="27">
+        <v>0.44</v>
+      </c>
+      <c r="Q12" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="R12" s="27">
+        <v>0.24</v>
+      </c>
+      <c r="S12" s="27">
+        <v>0.17</v>
+      </c>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="13" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="K13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="M13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="N13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="O13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="P13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="R13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="S13" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
+      <c r="D13" s="28">
+        <v>0.08</v>
+      </c>
+      <c r="E13" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F13" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G13" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="H13" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="I13" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="J13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="K13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="L13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="M13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="N13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="O13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="P13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="Q13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="R13" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="S13" s="27">
+        <v>0.04</v>
+      </c>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="18"/>
+      <c r="Y13" s="18"/>
+      <c r="Z13" s="18"/>
+      <c r="AA13" s="18"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="13" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" s="17">
-        <v>45789</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="O14" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="P14" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q14" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="R14" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="S14" s="18" t="s">
-        <v>215</v>
+      <c r="D14" s="28">
+        <v>12.77</v>
+      </c>
+      <c r="E14" s="27">
+        <v>12.74</v>
+      </c>
+      <c r="F14" s="27">
+        <v>12.86</v>
+      </c>
+      <c r="G14" s="27">
+        <v>12.8</v>
+      </c>
+      <c r="H14" s="27">
+        <v>12.29</v>
+      </c>
+      <c r="I14" s="27">
+        <v>12.5</v>
+      </c>
+      <c r="J14" s="27">
+        <v>11.4</v>
+      </c>
+      <c r="K14" s="27">
+        <v>11.25</v>
+      </c>
+      <c r="L14" s="27">
+        <v>11.15</v>
+      </c>
+      <c r="M14" s="27">
+        <v>10.92</v>
+      </c>
+      <c r="N14" s="27">
+        <v>10.81</v>
+      </c>
+      <c r="O14" s="27">
+        <v>10.61</v>
+      </c>
+      <c r="P14" s="27">
+        <v>10.48</v>
+      </c>
+      <c r="Q14" s="27">
+        <v>10.24</v>
+      </c>
+      <c r="R14" s="27">
+        <v>10.34</v>
+      </c>
+      <c r="S14" s="27">
+        <v>10.050000000000001</v>
       </c>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -1949,58 +1360,58 @@
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="13" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="17">
-        <v>45732</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="M15" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="N15" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="O15" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="P15" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q15" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="R15" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="S15" s="18" t="s">
-        <v>216</v>
+      <c r="D15" s="28">
+        <v>16.22</v>
+      </c>
+      <c r="E15" s="27">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="F15" s="27">
+        <v>16.3</v>
+      </c>
+      <c r="G15" s="27">
+        <v>16.39</v>
+      </c>
+      <c r="H15" s="27">
+        <v>16.62</v>
+      </c>
+      <c r="I15" s="27">
+        <v>15.9</v>
+      </c>
+      <c r="J15" s="27">
+        <v>15.83</v>
+      </c>
+      <c r="K15" s="27">
+        <v>15.94</v>
+      </c>
+      <c r="L15" s="27">
+        <v>16.32</v>
+      </c>
+      <c r="M15" s="27">
+        <v>16.86</v>
+      </c>
+      <c r="N15" s="27">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="O15" s="27">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="P15" s="27">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="Q15" s="27">
+        <v>17.77</v>
+      </c>
+      <c r="R15" s="27">
+        <v>18.21</v>
+      </c>
+      <c r="S15" s="27">
+        <v>18.3</v>
       </c>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -2014,58 +1425,58 @@
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="13" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="J16" s="17">
-        <v>45663</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="M16" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="N16" s="17">
-        <v>45905</v>
-      </c>
-      <c r="O16" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="P16" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q16" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="R16" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="S16" s="18" t="s">
-        <v>217</v>
+      <c r="D16" s="28">
+        <v>3</v>
+      </c>
+      <c r="E16" s="27">
+        <v>2.98</v>
+      </c>
+      <c r="F16" s="27">
+        <v>2.96</v>
+      </c>
+      <c r="G16" s="27">
+        <v>3.19</v>
+      </c>
+      <c r="H16" s="27">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="I16" s="27">
+        <v>4.97</v>
+      </c>
+      <c r="J16" s="27">
+        <v>6.1</v>
+      </c>
+      <c r="K16" s="27">
+        <v>6.3</v>
+      </c>
+      <c r="L16" s="27">
+        <v>6.38</v>
+      </c>
+      <c r="M16" s="27">
+        <v>6.44</v>
+      </c>
+      <c r="N16" s="27">
+        <v>5.9</v>
+      </c>
+      <c r="O16" s="27">
+        <v>5.2</v>
+      </c>
+      <c r="P16" s="27">
+        <v>5.15</v>
+      </c>
+      <c r="Q16" s="27">
+        <v>6.7</v>
+      </c>
+      <c r="R16" s="27">
+        <v>6.82</v>
+      </c>
+      <c r="S16" s="27">
+        <v>7.08</v>
       </c>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -2079,58 +1490,58 @@
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="13" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="L17" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="N17" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="O17" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="P17" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q17" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="R17" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="S17" s="18" t="s">
-        <v>218</v>
+      <c r="D17" s="28">
+        <v>4.62</v>
+      </c>
+      <c r="E17" s="27">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="F17" s="27">
+        <v>4.78</v>
+      </c>
+      <c r="G17" s="27">
+        <v>4.82</v>
+      </c>
+      <c r="H17" s="27">
+        <v>4.84</v>
+      </c>
+      <c r="I17" s="27">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="J17" s="27">
+        <v>4.67</v>
+      </c>
+      <c r="K17" s="27">
+        <v>4.57</v>
+      </c>
+      <c r="L17" s="27">
+        <v>4.46</v>
+      </c>
+      <c r="M17" s="27">
+        <v>4.57</v>
+      </c>
+      <c r="N17" s="27">
+        <v>4.21</v>
+      </c>
+      <c r="O17" s="27">
+        <v>4.38</v>
+      </c>
+      <c r="P17" s="27">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="Q17" s="27">
+        <v>4.7</v>
+      </c>
+      <c r="R17" s="27">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S17" s="27">
+        <v>5.12</v>
       </c>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -2144,58 +1555,58 @@
     <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="13" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="I18" s="22">
-        <v>45934</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="L18" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="M18" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="N18" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="O18" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="P18" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q18" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="R18" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="S18" s="18" t="s">
-        <v>219</v>
+      <c r="D18" s="28">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="E18" s="27">
+        <v>4.32</v>
+      </c>
+      <c r="F18" s="27">
+        <v>4.42</v>
+      </c>
+      <c r="G18" s="27">
+        <v>4.41</v>
+      </c>
+      <c r="H18" s="27">
+        <v>4.22</v>
+      </c>
+      <c r="I18" s="27">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J18" s="27">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="K18" s="27">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="L18" s="27">
+        <v>4.53</v>
+      </c>
+      <c r="M18" s="27">
+        <v>4.78</v>
+      </c>
+      <c r="N18" s="27">
+        <v>5.61</v>
+      </c>
+      <c r="O18" s="27">
+        <v>5.57</v>
+      </c>
+      <c r="P18" s="27">
+        <v>5.53</v>
+      </c>
+      <c r="Q18" s="27">
+        <v>5.56</v>
+      </c>
+      <c r="R18" s="27">
+        <v>5.57</v>
+      </c>
+      <c r="S18" s="27">
+        <v>5.6</v>
       </c>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
@@ -2209,58 +1620,58 @@
     <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="13" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="M19" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="N19" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="O19" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="P19" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q19" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="R19" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="S19" s="18" t="s">
-        <v>220</v>
+      <c r="D19" s="28">
+        <v>1.59</v>
+      </c>
+      <c r="E19" s="27">
+        <v>1.53</v>
+      </c>
+      <c r="F19" s="27">
+        <v>1.62</v>
+      </c>
+      <c r="G19" s="27">
+        <v>1.64</v>
+      </c>
+      <c r="H19" s="27">
+        <v>1.55</v>
+      </c>
+      <c r="I19" s="27">
+        <v>1.57</v>
+      </c>
+      <c r="J19" s="27">
+        <v>1.59</v>
+      </c>
+      <c r="K19" s="27">
+        <v>1.61</v>
+      </c>
+      <c r="L19" s="27">
+        <v>1.57</v>
+      </c>
+      <c r="M19" s="27">
+        <v>1.62</v>
+      </c>
+      <c r="N19" s="27">
+        <v>1.78</v>
+      </c>
+      <c r="O19" s="27">
+        <v>1.73</v>
+      </c>
+      <c r="P19" s="27">
+        <v>1.71</v>
+      </c>
+      <c r="Q19" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="R19" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="S19" s="27">
+        <v>1.67</v>
       </c>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
@@ -2274,58 +1685,58 @@
     <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="13" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="H20" s="22">
-        <v>45966</v>
-      </c>
-      <c r="I20" s="17">
-        <v>45782</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="M20" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="N20" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="O20" s="22">
-        <v>45935</v>
-      </c>
-      <c r="P20" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q20" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="R20" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="S20" s="18" t="s">
-        <v>120</v>
+      <c r="D20" s="28">
+        <v>5.52</v>
+      </c>
+      <c r="E20" s="27">
+        <v>5.43</v>
+      </c>
+      <c r="F20" s="27">
+        <v>5.32</v>
+      </c>
+      <c r="G20" s="27">
+        <v>5.18</v>
+      </c>
+      <c r="H20" s="27">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="I20" s="27">
+        <v>5.5</v>
+      </c>
+      <c r="J20" s="27">
+        <v>4.96</v>
+      </c>
+      <c r="K20" s="27">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="L20" s="27">
+        <v>4.88</v>
+      </c>
+      <c r="M20" s="27">
+        <v>4.87</v>
+      </c>
+      <c r="N20" s="27">
+        <v>5.29</v>
+      </c>
+      <c r="O20" s="27">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P20" s="27">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="Q20" s="27">
+        <v>4.67</v>
+      </c>
+      <c r="R20" s="27">
+        <v>4.53</v>
+      </c>
+      <c r="S20" s="27">
+        <v>4.32</v>
       </c>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
@@ -2339,58 +1750,58 @@
     <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="13" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" s="22">
-        <v>45935</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="M21" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="N21" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="O21" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="P21" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q21" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="R21" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="S21" s="18" t="s">
-        <v>221</v>
+      <c r="D21" s="28">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E21" s="27">
+        <v>4.41</v>
+      </c>
+      <c r="F21" s="27">
+        <v>4.43</v>
+      </c>
+      <c r="G21" s="27">
+        <v>4.51</v>
+      </c>
+      <c r="H21" s="27">
+        <v>4.53</v>
+      </c>
+      <c r="I21" s="27">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J21" s="27">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="K21" s="27">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="L21" s="27">
+        <v>5.28</v>
+      </c>
+      <c r="M21" s="27">
+        <v>5.7</v>
+      </c>
+      <c r="N21" s="27">
+        <v>5.99</v>
+      </c>
+      <c r="O21" s="27">
+        <v>5.69</v>
+      </c>
+      <c r="P21" s="27">
+        <v>5.69</v>
+      </c>
+      <c r="Q21" s="27">
+        <v>5.85</v>
+      </c>
+      <c r="R21" s="27">
+        <v>5.85</v>
+      </c>
+      <c r="S21" s="27">
+        <v>5.95</v>
       </c>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
@@ -2404,58 +1815,58 @@
     <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="13" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="L22" s="17">
-        <v>45692</v>
-      </c>
-      <c r="M22" s="17">
-        <v>45873</v>
-      </c>
-      <c r="N22" s="17">
-        <v>45904</v>
-      </c>
-      <c r="O22" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="P22" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q22" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="R22" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="S22" s="18" t="s">
-        <v>222</v>
+      <c r="D22" s="28">
+        <v>4</v>
+      </c>
+      <c r="E22" s="27">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F22" s="27">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="G22" s="27">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H22" s="27">
+        <v>4.29</v>
+      </c>
+      <c r="I22" s="27">
+        <v>4.25</v>
+      </c>
+      <c r="J22" s="27">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="K22" s="27">
+        <v>3.79</v>
+      </c>
+      <c r="L22" s="27">
+        <v>4.2</v>
+      </c>
+      <c r="M22" s="27">
+        <v>4.8</v>
+      </c>
+      <c r="N22" s="27">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O22" s="27">
+        <v>3.72</v>
+      </c>
+      <c r="P22" s="27">
+        <v>3.5</v>
+      </c>
+      <c r="Q22" s="27">
+        <v>3.29</v>
+      </c>
+      <c r="R22" s="27">
+        <v>3.26</v>
+      </c>
+      <c r="S22" s="27">
+        <v>3.25</v>
       </c>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
@@ -2469,58 +1880,58 @@
     <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="13" t="s">
-        <v>174</v>
+        <v>22</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="M23" s="17">
-        <v>45664</v>
-      </c>
-      <c r="N23" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="O23" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="P23" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q23" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="R23" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="S23" s="18" t="s">
-        <v>223</v>
+      <c r="D23" s="28">
+        <v>6.88</v>
+      </c>
+      <c r="E23" s="27">
+        <v>6.77</v>
+      </c>
+      <c r="F23" s="27">
+        <v>6.84</v>
+      </c>
+      <c r="G23" s="27">
+        <v>6.88</v>
+      </c>
+      <c r="H23" s="27">
+        <v>7</v>
+      </c>
+      <c r="I23" s="27">
+        <v>7.38</v>
+      </c>
+      <c r="J23" s="27">
+        <v>7.68</v>
+      </c>
+      <c r="K23" s="27">
+        <v>7.25</v>
+      </c>
+      <c r="L23" s="27">
+        <v>7.13</v>
+      </c>
+      <c r="M23" s="27">
+        <v>7.1</v>
+      </c>
+      <c r="N23" s="27">
+        <v>7.55</v>
+      </c>
+      <c r="O23" s="27">
+        <v>7.17</v>
+      </c>
+      <c r="P23" s="27">
+        <v>6.68</v>
+      </c>
+      <c r="Q23" s="27">
+        <v>6.2</v>
+      </c>
+      <c r="R23" s="27">
+        <v>6.13</v>
+      </c>
+      <c r="S23" s="27">
+        <v>6.43</v>
       </c>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -2534,58 +1945,58 @@
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="13" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="M24" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="N24" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="O24" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="P24" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q24" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="R24" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="S24" s="18" t="s">
-        <v>224</v>
+      <c r="D24" s="28">
+        <v>1.53</v>
+      </c>
+      <c r="E24" s="27">
+        <v>1.55</v>
+      </c>
+      <c r="F24" s="27">
+        <v>1.6</v>
+      </c>
+      <c r="G24" s="27">
+        <v>1.64</v>
+      </c>
+      <c r="H24" s="27">
+        <v>1.64</v>
+      </c>
+      <c r="I24" s="27">
+        <v>1.65</v>
+      </c>
+      <c r="J24" s="27">
+        <v>1.69</v>
+      </c>
+      <c r="K24" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="L24" s="27">
+        <v>1.73</v>
+      </c>
+      <c r="M24" s="27">
+        <v>1.74</v>
+      </c>
+      <c r="N24" s="27">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="O24" s="27">
+        <v>2.25</v>
+      </c>
+      <c r="P24" s="27">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q24" s="27">
+        <v>2.29</v>
+      </c>
+      <c r="R24" s="27">
+        <v>2.29</v>
+      </c>
+      <c r="S24" s="27">
+        <v>2.31</v>
       </c>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -2599,58 +2010,58 @@
     <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="13" t="s">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="M25" s="17">
-        <v>45691</v>
-      </c>
-      <c r="N25" s="17">
-        <v>45811</v>
-      </c>
-      <c r="O25" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="P25" s="17">
-        <v>45841</v>
-      </c>
-      <c r="Q25" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="R25" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="S25" s="18" t="s">
-        <v>225</v>
+      <c r="D25" s="28">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="E25" s="27">
+        <v>2.39</v>
+      </c>
+      <c r="F25" s="27">
+        <v>2.41</v>
+      </c>
+      <c r="G25" s="27">
+        <v>2.54</v>
+      </c>
+      <c r="H25" s="27">
+        <v>2.57</v>
+      </c>
+      <c r="I25" s="27">
+        <v>2.64</v>
+      </c>
+      <c r="J25" s="27">
+        <v>2.7</v>
+      </c>
+      <c r="K25" s="27">
+        <v>2.83</v>
+      </c>
+      <c r="L25" s="27">
+        <v>2.88</v>
+      </c>
+      <c r="M25" s="27">
+        <v>3.2</v>
+      </c>
+      <c r="N25" s="27">
+        <v>3.6</v>
+      </c>
+      <c r="O25" s="27">
+        <v>2.81</v>
+      </c>
+      <c r="P25" s="27">
+        <v>3.7</v>
+      </c>
+      <c r="Q25" s="27">
+        <v>3.31</v>
+      </c>
+      <c r="R25" s="27">
+        <v>3.32</v>
+      </c>
+      <c r="S25" s="27">
+        <v>3.39</v>
       </c>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -2669,53 +2080,53 @@
       <c r="C26" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="I26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="K26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="M26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="N26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="O26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="P26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="R26" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="S26" s="18" t="s">
-        <v>209</v>
+      <c r="D26" s="28">
+        <v>100</v>
+      </c>
+      <c r="E26" s="27">
+        <v>100</v>
+      </c>
+      <c r="F26" s="27">
+        <v>100</v>
+      </c>
+      <c r="G26" s="27">
+        <v>100</v>
+      </c>
+      <c r="H26" s="27">
+        <v>100</v>
+      </c>
+      <c r="I26" s="27">
+        <v>100</v>
+      </c>
+      <c r="J26" s="27">
+        <v>100</v>
+      </c>
+      <c r="K26" s="27">
+        <v>100</v>
+      </c>
+      <c r="L26" s="27">
+        <v>100</v>
+      </c>
+      <c r="M26" s="27">
+        <v>100</v>
+      </c>
+      <c r="N26" s="27">
+        <v>100</v>
+      </c>
+      <c r="O26" s="27">
+        <v>100</v>
+      </c>
+      <c r="P26" s="27">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="27">
+        <v>100</v>
+      </c>
+      <c r="R26" s="27">
+        <v>100</v>
+      </c>
+      <c r="S26" s="27">
+        <v>100</v>
       </c>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
